--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E648"/>
+  <dimension ref="A1:E649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14040,6 +14040,27 @@
         <v>399.19</v>
       </c>
       <c r="E648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>353.81</v>
+      </c>
+      <c r="C649" t="n">
+        <v>348.28</v>
+      </c>
+      <c r="D649" t="n">
+        <v>392.84</v>
+      </c>
+      <c r="E649" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14056,7 +14077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B758"/>
+  <dimension ref="A1:B759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21639,6 +21660,16 @@
       </c>
       <c r="B758" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-0.41</v>
       </c>
     </row>
   </sheetData>
@@ -21807,28 +21838,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2824077736924565</v>
+        <v>0.2811976584312469</v>
       </c>
       <c r="J2" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K2" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08368128116461837</v>
+        <v>0.08321556414085618</v>
       </c>
       <c r="M2" t="n">
-        <v>5.677552831788523</v>
+        <v>5.675695118712063</v>
       </c>
       <c r="N2" t="n">
-        <v>50.22172338277721</v>
+        <v>50.17183195871335</v>
       </c>
       <c r="O2" t="n">
-        <v>7.086728679918346</v>
+        <v>7.083207744991908</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6017352161826</v>
+        <v>350.6142138645208</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21885,28 +21916,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4558244991056195</v>
+        <v>0.4529372478236335</v>
       </c>
       <c r="J3" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K3" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1815402171739927</v>
+        <v>0.1796789952632252</v>
       </c>
       <c r="M3" t="n">
-        <v>5.87923605364802</v>
+        <v>5.886585926065972</v>
       </c>
       <c r="N3" t="n">
-        <v>53.86912231709841</v>
+        <v>53.94317249185895</v>
       </c>
       <c r="O3" t="n">
-        <v>7.339558727682367</v>
+        <v>7.344601588368082</v>
       </c>
       <c r="P3" t="n">
-        <v>346.3771500985631</v>
+        <v>346.4069232900654</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21963,28 +21994,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.564634361087301</v>
+        <v>0.5667582062496532</v>
       </c>
       <c r="J4" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K4" t="n">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03591140908363133</v>
+        <v>0.03627271506783036</v>
       </c>
       <c r="M4" t="n">
-        <v>17.70012985443871</v>
+        <v>17.68540056029204</v>
       </c>
       <c r="N4" t="n">
-        <v>492.1972515943672</v>
+        <v>491.5227386686801</v>
       </c>
       <c r="O4" t="n">
-        <v>22.18551896157418</v>
+        <v>22.17031210129167</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5104948776502</v>
+        <v>370.4885938920537</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22022,7 +22053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E648"/>
+  <dimension ref="A1:E649"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39521,6 +39552,33 @@
         </is>
       </c>
     </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-37.16590227137098,175.8814874695194</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-37.16662079207373,175.88149753833494</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-37.1672942926825,175.8820685371198</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E649"/>
+  <dimension ref="A1:E651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14061,6 +14061,48 @@
         <v>392.84</v>
       </c>
       <c r="E649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="C650" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="D650" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>355.23</v>
+      </c>
+      <c r="C651" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="D651" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="E651" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14077,7 +14119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B759"/>
+  <dimension ref="A1:B761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21670,6 +21712,26 @@
       </c>
       <c r="B759" t="n">
         <v>-0.41</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>
@@ -21838,28 +21900,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2811976584312469</v>
+        <v>0.2792296936960417</v>
       </c>
       <c r="J2" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K2" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08321556414085618</v>
+        <v>0.08255470045623237</v>
       </c>
       <c r="M2" t="n">
-        <v>5.675695118712063</v>
+        <v>5.669367399070834</v>
       </c>
       <c r="N2" t="n">
-        <v>50.17183195871335</v>
+        <v>50.05525086058558</v>
       </c>
       <c r="O2" t="n">
-        <v>7.083207744991908</v>
+        <v>7.074973559002577</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6142138645208</v>
+        <v>350.6345609144293</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21916,28 +21978,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4529372478236335</v>
+        <v>0.4466186090251089</v>
       </c>
       <c r="J3" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K3" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1796789952632252</v>
+        <v>0.1754490412317179</v>
       </c>
       <c r="M3" t="n">
-        <v>5.886585926065972</v>
+        <v>5.904214080555542</v>
       </c>
       <c r="N3" t="n">
-        <v>53.94317249185895</v>
+        <v>54.15370806396455</v>
       </c>
       <c r="O3" t="n">
-        <v>7.344601588368082</v>
+        <v>7.358920305585905</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4069232900654</v>
+        <v>346.4722594580687</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -21994,28 +22056,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5667582062496532</v>
+        <v>0.5658542675956879</v>
       </c>
       <c r="J4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03627271506783036</v>
+        <v>0.03637421102979144</v>
       </c>
       <c r="M4" t="n">
-        <v>17.68540056029204</v>
+        <v>17.63534699704239</v>
       </c>
       <c r="N4" t="n">
-        <v>491.5227386686801</v>
+        <v>490.0180659226695</v>
       </c>
       <c r="O4" t="n">
-        <v>22.17031210129167</v>
+        <v>22.13635168501507</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4885938920537</v>
+        <v>370.4979409024934</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22053,7 +22115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E649"/>
+  <dimension ref="A1:E651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39579,6 +39641,60 @@
         </is>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-16 22:06:24+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-37.16590215455034,175.88148892529347</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-37.166621807516336,175.88148488417903</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-37.16730234478569,175.88196819893201</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-25 22:00:16+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-37.165900995329075,175.88150337105117</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-37.16662160083343,175.8814874598037</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-37.16730234478569,175.88196819893201</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E651"/>
+  <dimension ref="A1:E654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14103,6 +14103,69 @@
         <v>383.88</v>
       </c>
       <c r="E651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="C652" t="n">
+        <v>347.15</v>
+      </c>
+      <c r="D652" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>355.57</v>
+      </c>
+      <c r="C653" t="n">
+        <v>347.88</v>
+      </c>
+      <c r="D653" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>356.39</v>
+      </c>
+      <c r="C654" t="n">
+        <v>348.59</v>
+      </c>
+      <c r="D654" t="n">
+        <v>381.08</v>
+      </c>
+      <c r="E654" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14119,7 +14182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B761"/>
+  <dimension ref="A1:B764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21732,6 +21795,36 @@
       </c>
       <c r="B761" t="n">
         <v>0.7</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -21900,28 +21993,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2792296936960417</v>
+        <v>0.2773032469745865</v>
       </c>
       <c r="J2" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K2" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08255470045623237</v>
+        <v>0.08215905460604178</v>
       </c>
       <c r="M2" t="n">
-        <v>5.669367399070834</v>
+        <v>5.654121998104435</v>
       </c>
       <c r="N2" t="n">
-        <v>50.05525086058558</v>
+        <v>49.84984397195869</v>
       </c>
       <c r="O2" t="n">
-        <v>7.074973559002577</v>
+        <v>7.060442193797686</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6345609144293</v>
+        <v>350.6545259802356</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -21978,28 +22071,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4466186090251089</v>
+        <v>0.4378096221364796</v>
       </c>
       <c r="J3" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K3" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1754490412317179</v>
+        <v>0.1697569799729289</v>
       </c>
       <c r="M3" t="n">
-        <v>5.904214080555542</v>
+        <v>5.926687680305379</v>
       </c>
       <c r="N3" t="n">
-        <v>54.15370806396455</v>
+        <v>54.39889727808775</v>
       </c>
       <c r="O3" t="n">
-        <v>7.358920305585905</v>
+        <v>7.37556081109008</v>
       </c>
       <c r="P3" t="n">
-        <v>346.4722594580687</v>
+        <v>346.5635576518355</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22056,28 +22149,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5658542675956879</v>
+        <v>0.5624376136775459</v>
       </c>
       <c r="J4" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="K4" t="n">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03637421102979144</v>
+        <v>0.03626352118530474</v>
       </c>
       <c r="M4" t="n">
-        <v>17.63534699704239</v>
+        <v>17.57085918605192</v>
       </c>
       <c r="N4" t="n">
-        <v>490.0180659226695</v>
+        <v>487.8417209930134</v>
       </c>
       <c r="O4" t="n">
-        <v>22.13635168501507</v>
+        <v>22.08713926684516</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4979409024934</v>
+        <v>370.5333544737898</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22115,7 +22208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E651"/>
+  <dimension ref="A1:E654"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39695,6 +39788,87 @@
         </is>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-02 22:00:02+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-37.165900950398,175.88150393096421</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-37.166621807516336,175.88148488417903</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-37.167304016305486,175.8819473697959</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-37.1659006897976,175.88150717846005</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-37.16662115152259,175.88149305898776</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-37.16730474422427,175.88193829904273</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 22:00:09+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-37.16589995292709,175.88151636103436</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-37.16662051350075,175.88150100982898</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-37.16730486105067,175.88193684324284</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E654"/>
+  <dimension ref="A1:E655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14166,6 +14166,27 @@
         <v>381.08</v>
       </c>
       <c r="E654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>357.31</v>
+      </c>
+      <c r="C655" t="n">
+        <v>350.68</v>
+      </c>
+      <c r="D655" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="E655" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14182,7 +14203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B764"/>
+  <dimension ref="A1:B765"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21825,6 +21846,16 @@
       </c>
       <c r="B764" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B765" t="n">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -21993,28 +22024,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2773032469745865</v>
+        <v>0.2770984327549028</v>
       </c>
       <c r="J2" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K2" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08215905460604178</v>
+        <v>0.08227744373360502</v>
       </c>
       <c r="M2" t="n">
-        <v>5.654121998104435</v>
+        <v>5.646610330064734</v>
       </c>
       <c r="N2" t="n">
-        <v>49.84984397195869</v>
+        <v>49.774415786603</v>
       </c>
       <c r="O2" t="n">
-        <v>7.060442193797686</v>
+        <v>7.055098566753196</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6545259802356</v>
+        <v>350.6566606368524</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22071,28 +22102,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4378096221364796</v>
+        <v>0.4356763899307783</v>
       </c>
       <c r="J3" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K3" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1697569799729289</v>
+        <v>0.1685914524621894</v>
       </c>
       <c r="M3" t="n">
-        <v>5.926687680305379</v>
+        <v>5.929559043646949</v>
       </c>
       <c r="N3" t="n">
-        <v>54.39889727808775</v>
+        <v>54.40194162171103</v>
       </c>
       <c r="O3" t="n">
-        <v>7.37556081109008</v>
+        <v>7.375767188686953</v>
       </c>
       <c r="P3" t="n">
-        <v>346.5635576518355</v>
+        <v>346.5857910604826</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22149,28 +22180,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5624376136775459</v>
+        <v>0.5564497867874602</v>
       </c>
       <c r="J4" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="K4" t="n">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03626352118530474</v>
+        <v>0.03557999952876034</v>
       </c>
       <c r="M4" t="n">
-        <v>17.57085918605192</v>
+        <v>17.57269765182575</v>
       </c>
       <c r="N4" t="n">
-        <v>487.8417209930134</v>
+        <v>487.7751234233897</v>
       </c>
       <c r="O4" t="n">
-        <v>22.08713926684516</v>
+        <v>22.08563160571573</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5333544737898</v>
+        <v>370.5957620268915</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22208,7 +22239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E654"/>
+  <dimension ref="A1:E655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39869,6 +39900,33 @@
         </is>
       </c>
     </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-18 22:06:10+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-37.16589912619348,175.88152666343447</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-37.16661863537707,175.8815244144169</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-37.16731988657609,175.88174960492978</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E655"/>
+  <dimension ref="A1:E657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14187,6 +14187,48 @@
         <v>364.36</v>
       </c>
       <c r="E655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="n">
+        <v>360.1</v>
+      </c>
+      <c r="C656" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="D656" t="n">
+        <v>366.99</v>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="C657" t="n">
+        <v>353.08</v>
+      </c>
+      <c r="D657" t="n">
+        <v>367.33</v>
+      </c>
+      <c r="E657" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14203,7 +14245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B765"/>
+  <dimension ref="A1:B767"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21856,6 +21898,26 @@
       </c>
       <c r="B765" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B766" t="n">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-03-15 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B767" t="n">
+        <v>-0.46</v>
       </c>
     </row>
   </sheetData>
@@ -22024,28 +22086,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2770984327549028</v>
+        <v>0.278316419955827</v>
       </c>
       <c r="J2" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K2" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08227744373360502</v>
+        <v>0.08338720360304042</v>
       </c>
       <c r="M2" t="n">
-        <v>5.646610330064734</v>
+        <v>5.635748792155764</v>
       </c>
       <c r="N2" t="n">
-        <v>49.774415786603</v>
+        <v>49.63677141153553</v>
       </c>
       <c r="O2" t="n">
-        <v>7.055098566753196</v>
+        <v>7.045336855788766</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6566606368524</v>
+        <v>350.6439382805565</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22102,28 +22164,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4356763899307783</v>
+        <v>0.4328668108206483</v>
       </c>
       <c r="J3" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K3" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1685914524621894</v>
+        <v>0.1674450538039081</v>
       </c>
       <c r="M3" t="n">
-        <v>5.929559043646949</v>
+        <v>5.927218984584981</v>
       </c>
       <c r="N3" t="n">
-        <v>54.40194162171103</v>
+        <v>54.31109007154242</v>
       </c>
       <c r="O3" t="n">
-        <v>7.375767188686953</v>
+        <v>7.369605828776898</v>
       </c>
       <c r="P3" t="n">
-        <v>346.5857910604826</v>
+        <v>346.6151378418008</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22180,28 +22242,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5564497867874602</v>
+        <v>0.5461527962374146</v>
       </c>
       <c r="J4" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K4" t="n">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03557999952876034</v>
+        <v>0.03445469638833198</v>
       </c>
       <c r="M4" t="n">
-        <v>17.57269765182575</v>
+        <v>17.56822104028113</v>
       </c>
       <c r="N4" t="n">
-        <v>487.7751234233897</v>
+        <v>487.2949517945285</v>
       </c>
       <c r="O4" t="n">
-        <v>22.08563160571573</v>
+        <v>22.07475824996796</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5957620268915</v>
+        <v>370.7033123379669</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22239,7 +22301,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E655"/>
+  <dimension ref="A1:E657"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39927,6 +39989,60 @@
         </is>
       </c>
     </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>-37.1658966190285,175.88155790658098</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>-37.16661624503122,175.88155420207218</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>-37.16731752313069,175.8817790568955</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-15 21:59:49+00:00</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>-37.16589644828937,175.88156003425036</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>-37.16661647867437,175.88155129049696</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>-37.1673172175897,175.8817828643738</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E657"/>
+  <dimension ref="A1:E659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14229,6 +14229,48 @@
         <v>367.33</v>
       </c>
       <c r="E657" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="n">
+        <v>361.17</v>
+      </c>
+      <c r="C658" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="D658" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="n">
+        <v>361.57</v>
+      </c>
+      <c r="C659" t="n">
+        <v>354.56</v>
+      </c>
+      <c r="D659" t="n">
+        <v>375.51</v>
+      </c>
+      <c r="E659" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14245,7 +14287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B767"/>
+  <dimension ref="A1:B770"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21918,6 +21960,36 @@
       </c>
       <c r="B767" t="n">
         <v>-0.46</v>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B768" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>2026-04-08 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B769" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>2026-04-16 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B770" t="n">
+        <v>-0.34</v>
       </c>
     </row>
   </sheetData>
@@ -22086,28 +22158,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.278316419955827</v>
+        <v>0.2801693574612171</v>
       </c>
       <c r="J2" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="K2" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08338720360304042</v>
+        <v>0.08483201783094252</v>
       </c>
       <c r="M2" t="n">
-        <v>5.635748792155764</v>
+        <v>5.628179815763963</v>
       </c>
       <c r="N2" t="n">
-        <v>49.63677141153553</v>
+        <v>49.51857673005811</v>
       </c>
       <c r="O2" t="n">
-        <v>7.045336855788766</v>
+        <v>7.036943706614265</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6439382805565</v>
+        <v>350.6245025227801</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22164,28 +22236,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4328668108206483</v>
+        <v>0.4306510359907721</v>
       </c>
       <c r="J3" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="K3" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1674450538039081</v>
+        <v>0.1667513112558021</v>
       </c>
       <c r="M3" t="n">
-        <v>5.927218984584981</v>
+        <v>5.921522589469078</v>
       </c>
       <c r="N3" t="n">
-        <v>54.31109007154242</v>
+        <v>54.1928809244756</v>
       </c>
       <c r="O3" t="n">
-        <v>7.369605828776898</v>
+        <v>7.361581414646964</v>
       </c>
       <c r="P3" t="n">
-        <v>346.6151378418008</v>
+        <v>346.6383760143151</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22242,28 +22314,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5461527962374146</v>
+        <v>0.5386539641541673</v>
       </c>
       <c r="J4" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="K4" t="n">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03445469638833198</v>
+        <v>0.03370802059995492</v>
       </c>
       <c r="M4" t="n">
-        <v>17.56822104028113</v>
+        <v>17.55052334535393</v>
       </c>
       <c r="N4" t="n">
-        <v>487.2949517945285</v>
+        <v>486.3856013568856</v>
       </c>
       <c r="O4" t="n">
-        <v>22.07475824996796</v>
+        <v>22.05415156737809</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7033123379669</v>
+        <v>370.7819407849208</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22301,7 +22373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E657"/>
+  <dimension ref="A1:E659"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40043,6 +40115,60 @@
         </is>
       </c>
     </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>-37.1658956574971,175.8815698887189</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>-37.16661570585442,175.88156092109182</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>-37.167316211100854,175.88179540665496</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16 21:59:37+00:00</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>-37.1658952980458,175.8815743680227</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>-37.16661514870468,175.88156786407868</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>-37.16730986659619,175.8818744678104</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E659"/>
+  <dimension ref="A1:E663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14268,9 +14268,93 @@
         <v>354.56</v>
       </c>
       <c r="D659" t="n">
-        <v>375.51</v>
+        <v>368.45</v>
       </c>
       <c r="E659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="n">
+        <v>361.85</v>
+      </c>
+      <c r="C660" t="n">
+        <v>355.05</v>
+      </c>
+      <c r="D660" t="n">
+        <v>368.45</v>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="n">
+        <v>361.34</v>
+      </c>
+      <c r="C661" t="n">
+        <v>355.03</v>
+      </c>
+      <c r="D661" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>361.06</v>
+      </c>
+      <c r="C662" t="n">
+        <v>354.99</v>
+      </c>
+      <c r="D662" t="n">
+        <v>368.7</v>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>360.34</v>
+      </c>
+      <c r="C663" t="n">
+        <v>355.51</v>
+      </c>
+      <c r="D663" t="n">
+        <v>371.57</v>
+      </c>
+      <c r="E663" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14287,7 +14371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B770"/>
+  <dimension ref="A1:B774"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21990,6 +22074,46 @@
       </c>
       <c r="B770" t="n">
         <v>-0.34</v>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>2026-04-24 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B771" t="n">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>2026-05-18 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B773" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B774" t="n">
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -22158,28 +22282,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2801693574612171</v>
+        <v>0.2835267355694692</v>
       </c>
       <c r="J2" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="K2" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08483201783094252</v>
+        <v>0.08758765148996772</v>
       </c>
       <c r="M2" t="n">
-        <v>5.628179815763963</v>
+        <v>5.611265802903193</v>
       </c>
       <c r="N2" t="n">
-        <v>49.51857673005811</v>
+        <v>49.2749321186574</v>
       </c>
       <c r="O2" t="n">
-        <v>7.036943706614265</v>
+        <v>7.019610538958511</v>
       </c>
       <c r="P2" t="n">
-        <v>350.6245025227801</v>
+        <v>350.5891342791519</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22236,28 +22360,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4306510359907721</v>
+        <v>0.4272517438031683</v>
       </c>
       <c r="J3" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="K3" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1667513112558021</v>
+        <v>0.1661147446443836</v>
       </c>
       <c r="M3" t="n">
-        <v>5.921522589469078</v>
+        <v>5.904358378926261</v>
       </c>
       <c r="N3" t="n">
-        <v>54.1928809244756</v>
+        <v>53.92070061135318</v>
       </c>
       <c r="O3" t="n">
-        <v>7.361581414646964</v>
+        <v>7.343071606034711</v>
       </c>
       <c r="P3" t="n">
-        <v>346.6383760143151</v>
+        <v>346.6741930436466</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22314,28 +22438,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5386539641541673</v>
+        <v>0.5189288720918217</v>
       </c>
       <c r="J4" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="K4" t="n">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03370802059995492</v>
+        <v>0.03162260939433781</v>
       </c>
       <c r="M4" t="n">
-        <v>17.55052334535393</v>
+        <v>17.53849911884799</v>
       </c>
       <c r="N4" t="n">
-        <v>486.3856013568856</v>
+        <v>485.2352395800373</v>
       </c>
       <c r="O4" t="n">
-        <v>22.05415156737809</v>
+        <v>22.02805573762781</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7819407849208</v>
+        <v>370.9896982672694</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22373,7 +22497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E659"/>
+  <dimension ref="A1:E663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40160,10 +40284,118 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>-37.16730986659619,175.8818744678104</t>
+          <t>-37.167316211100854,175.88179540665496</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-24 21:59:24+00:00</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>-37.16589504642981,175.88157750353534</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>-37.16661470837638,175.88157335127786</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>-37.167316211100854,175.88179540665496</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>-37.16589550473032,175.88157179242305</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>-37.166614726348975,175.88157312731056</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>-37.167316130222225,175.8817964145168</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-18 21:59:13+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>-37.165895756346195,175.88156865691036</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>-37.16661476229415,175.88157267937592</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>-37.16731598643798,175.8817982062712</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>-37.165896403358005,175.88156059416335</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>-37.16661429500672,175.88157850252603</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>-37.16731340730353,175.88183034586456</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0193/nzd0193.xlsx
+++ b/data/nzd0193/nzd0193.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E663"/>
+  <dimension ref="A1:E667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14355,6 +14355,90 @@
         <v>371.57</v>
       </c>
       <c r="E663" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>358.75</v>
+      </c>
+      <c r="C664" t="n">
+        <v>354.83</v>
+      </c>
+      <c r="D664" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="C665" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="D665" t="n">
+        <v>372.28</v>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>358.03</v>
+      </c>
+      <c r="C666" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="D666" t="n">
+        <v>372.93</v>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>356.61</v>
+      </c>
+      <c r="C667" t="n">
+        <v>355.28</v>
+      </c>
+      <c r="D667" t="n">
+        <v>372.01</v>
+      </c>
+      <c r="E667" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14371,7 +14455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B774"/>
+  <dimension ref="A1:B778"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22114,6 +22198,46 @@
       </c>
       <c r="B774" t="n">
         <v>-0.53</v>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B775" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B776" t="n">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>2026-06-19 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B777" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B778" t="n">
+        <v>-0.66</v>
       </c>
     </row>
   </sheetData>
@@ -22282,28 +22406,28 @@
         <v>0.0914</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2835267355694692</v>
+        <v>0.283268765954221</v>
       </c>
       <c r="J2" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="K2" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08758765148996772</v>
+        <v>0.08841184510433486</v>
       </c>
       <c r="M2" t="n">
-        <v>5.611265802903193</v>
+        <v>5.581685796659177</v>
       </c>
       <c r="N2" t="n">
-        <v>49.2749321186574</v>
+        <v>48.98356988085193</v>
       </c>
       <c r="O2" t="n">
-        <v>7.019610538958511</v>
+        <v>6.998826321666507</v>
       </c>
       <c r="P2" t="n">
-        <v>350.5891342791519</v>
+        <v>350.5918741571605</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -22360,28 +22484,28 @@
         <v>0.0677</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4272517438031683</v>
+        <v>0.4243267678223551</v>
       </c>
       <c r="J3" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="K3" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1661147446443836</v>
+        <v>0.1657886078314201</v>
       </c>
       <c r="M3" t="n">
-        <v>5.904358378926261</v>
+        <v>5.884714197130006</v>
       </c>
       <c r="N3" t="n">
-        <v>53.92070061135318</v>
+        <v>53.63979665065459</v>
       </c>
       <c r="O3" t="n">
-        <v>7.343071606034711</v>
+        <v>7.323919486904167</v>
       </c>
       <c r="P3" t="n">
-        <v>346.6741930436466</v>
+        <v>346.7051365382858</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -22438,28 +22562,28 @@
         <v>0.1102</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5189288720918217</v>
+        <v>0.5050277688633811</v>
       </c>
       <c r="J4" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="K4" t="n">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03162260939433781</v>
+        <v>0.0303009347772325</v>
       </c>
       <c r="M4" t="n">
-        <v>17.53849911884799</v>
+        <v>17.49925778706056</v>
       </c>
       <c r="N4" t="n">
-        <v>485.2352395800373</v>
+        <v>483.2549371879931</v>
       </c>
       <c r="O4" t="n">
-        <v>22.02805573762781</v>
+        <v>21.98306023255163</v>
       </c>
       <c r="P4" t="n">
-        <v>370.9896982672694</v>
+        <v>371.1367725951406</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -22497,7 +22621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E663"/>
+  <dimension ref="A1:E667"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40401,6 +40525,114 @@
         </is>
       </c>
     </row>
+    <row r="664">
+      <c r="A664" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:05:07+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>-37.165897832173854,175.88154278892975</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>-37.166614906074834,175.88157088763742</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>-37.167312769258494,175.88183829677394</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>-37.165898002912684,175.88154066126032</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>-37.16661407933551,175.88158119013374</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>-37.167312769258494,175.88183829677394</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-19 21:59:15+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>-37.16589847918394,175.88153472618222</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>-37.1666136479929,175.88158656534907</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>-37.16731218513228,175.88184557577537</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>-37.16589975523,175.8815188246518</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>-37.16661450169158,175.88157592690195</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>-37.167313011895395,175.8818352731887</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
